--- a/data/trans_orig/Q21A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q21A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de veces que utilizó un servicios de urgencias en el último año</t>
+          <t>Número medio de veces que la población utilizó un servicios de urgencias en el último año (tasa de respuesta: 96,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,22 +721,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,01</t>
+          <t>1,54; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,72</t>
+          <t>1,42; 1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,98</t>
+          <t>1,67; 4,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,05</t>
+          <t>1,69; 2,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,27 +746,27 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,97</t>
+          <t>1,62; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,19</t>
+          <t>1,66; 2,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 1,83</t>
+          <t>1,6; 1,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 1,89</t>
+          <t>1,64; 1,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,84</t>
+          <t>1,58; 1,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,55</t>
+          <t>1,2; 1,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,21</t>
+          <t>1,53; 2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,89</t>
+          <t>1,5; 1,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,04</t>
+          <t>1,54; 1,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,92</t>
+          <t>1,53; 1,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,27</t>
+          <t>1,82; 2,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,33</t>
+          <t>1,8; 2,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,23</t>
+          <t>1,92; 11,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,66</t>
+          <t>1,41; 1,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,11</t>
+          <t>1,75; 2,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,05</t>
+          <t>1,7; 2,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 9,51</t>
+          <t>1,8; 10,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,49</t>
+          <t>1,15; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,15</t>
+          <t>1,3; 2,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,15</t>
+          <t>1,28; 3,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,06</t>
+          <t>1,39; 2,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,07</t>
+          <t>1,38; 2,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,6</t>
+          <t>1,53; 2,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,55</t>
+          <t>1,49; 2,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,91</t>
+          <t>1,69; 2,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,74</t>
+          <t>1,33; 1,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,18</t>
+          <t>1,52; 2,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,32</t>
+          <t>1,47; 2,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,3</t>
+          <t>1,61; 2,24</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,48</t>
+          <t>1,29; 1,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,93</t>
+          <t>1,58; 1,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,81</t>
+          <t>1,5; 1,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,12</t>
+          <t>1,61; 2,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,86</t>
+          <t>1,63; 1,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,04</t>
+          <t>1,78; 2,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,09</t>
+          <t>1,76; 2,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 9,2</t>
+          <t>1,91; 9,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,67</t>
+          <t>1,52; 1,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,78</t>
+          <t>1,85; 7,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q21A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q21A-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>1,98</t>
         </is>
       </c>
     </row>
@@ -716,32 +716,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,65</t>
+          <t>1,36; 1,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,02</t>
+          <t>1,53; 1,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,73</t>
+          <t>1,41; 1,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,21</t>
+          <t>1,69; 4,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,07</t>
+          <t>1,7; 2,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,96</t>
+          <t>1,64; 1,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,16</t>
+          <t>1,64; 2,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,84</t>
+          <t>1,61; 1,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 1,9</t>
+          <t>1,64; 1,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,83</t>
+          <t>1,57; 1,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,61</t>
+          <t>1,7; 2,52</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,53</t>
+          <t>1,2; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,15</t>
+          <t>1,55; 2,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,97</t>
+          <t>1,5; 1,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,97</t>
+          <t>1,55; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,93</t>
+          <t>1,54; 1,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,26</t>
+          <t>1,83; 2,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,32</t>
+          <t>1,78; 2,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,35</t>
+          <t>1,86; 2,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,65</t>
+          <t>1,42; 1,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,13</t>
+          <t>1,76; 2,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,01</t>
+          <t>1,75; 2,11</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,82</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,48</t>
+          <t>1,16; 1,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,16</t>
+          <t>1,32; 2,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,18</t>
+          <t>1,28; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,03</t>
+          <t>1,39; 2,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,06</t>
+          <t>1,39; 2,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,58</t>
+          <t>1,55; 2,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,58</t>
+          <t>1,48; 2,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,68</t>
+          <t>1,73; 2,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,71</t>
+          <t>1,32; 1,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,16</t>
+          <t>1,5; 2,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,41</t>
+          <t>1,46; 2,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,24</t>
+          <t>1,63; 2,19</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,49</t>
+          <t>1,28; 1,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,97</t>
+          <t>1,59; 1,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,82</t>
+          <t>1,5; 1,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,13</t>
+          <t>1,63; 2,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,87</t>
+          <t>1,64; 1,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,05</t>
+          <t>1,78; 2,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,12</t>
+          <t>1,76; 2,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,29</t>
+          <t>1,84; 2,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,7</t>
+          <t>1,51; 1,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 1,95</t>
+          <t>1,74; 1,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 1,92</t>
+          <t>1,68; 1,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,27</t>
+          <t>1,78; 2,07</t>
         </is>
       </c>
     </row>
